--- a/bot excution excels {flow}/DMS_Login.xlsx
+++ b/bot excution excels {flow}/DMS_Login.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <x:si>
     <x:t>1.1 Main Sequence (Sequence)</x:t>
   </x:si>
@@ -58,7 +58,7 @@
     <x:t>1.3 Do (Sequence)</x:t>
   </x:si>
   <x:si>
-    <x:t>1.4 CV Screen Scope 'BODY' (CVScope)</x:t>
+    <x:t>1.348 CV Screen Scope 'BODY' (CVScope)</x:t>
   </x:si>
   <x:si>
     <x:t>Target</x:t>
@@ -79,7 +79,7 @@
     <x:t>OCREngine</x:t>
   </x:si>
   <x:si>
-    <x:t>1.6 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+    <x:t>1.386 UiPathScreenOCR (UiPathScreenOCR)</x:t>
   </x:si>
   <x:si>
     <x:t>UseSeparateOcrProcess = True</x:t>
@@ -94,10 +94,10 @@
     <x:t>ResultType = System.Collections.Generic.IEnumerable`1[System.Collections.Generic.KeyValuePair`2[System.Drawing.Rectangle,System.String]]</x:t>
   </x:si>
   <x:si>
-    <x:t>1.5 Do (Sequence)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.6 CV Click - 'Inputbox' (CvClickWithDescriptor)</x:t>
+    <x:t>1.349 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.375 CV Click - 'Inputbox' (CvClickWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Descriptor = "Target: InputBox (34,298,446,41)" +
@@ -119,7 +119,7 @@
     <x:t>MouseButton = BTN_LEFT</x:t>
   </x:si>
   <x:si>
-    <x:t>1.6 CV Type Into - 'Inputbox' (CvTypeIntoWithDescriptor)</x:t>
+    <x:t>1.361 CV Type Into - 'Inputbox' (CvTypeIntoWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Text = "!Welcome123"</x:t>
@@ -134,32 +134,41 @@
     <x:t>Activate = True</x:t>
   </x:si>
   <x:si>
-    <x:t>1.6 CV Click - Text (CvClickWithDescriptor)</x:t>
+    <x:t>1.350 CV Click - Text (CvClickWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Descriptor = "Target: Text 'Sign In' (239,412,38,15)" +
 "Anchor: Button (35,398,446,41)"</x:t>
   </x:si>
   <x:si>
-    <x:t>1.4 Delay (Delay)</x:t>
+    <x:t>1.346 Delay (Delay)</x:t>
   </x:si>
   <x:si>
     <x:t>Duration = 00:00:03</x:t>
   </x:si>
   <x:si>
-    <x:t>1.4 CV Screen Scope 'firefox.exe  synergydms...' (CVScope)</x:t>
+    <x:t>1.321 CV Screen Scope 'firefox.exe  synergydms...' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.336 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.322 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.325 CV Click - Text (CvClickWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Descriptor = "Target: Text 'D' (25,18,16,18)"</x:t>
   </x:si>
   <x:si>
-    <x:t>1.6 Delay (Delay)</x:t>
+    <x:t>1.323 Delay (Delay)</x:t>
   </x:si>
   <x:si>
     <x:t>Duration = 00:00:02</x:t>
   </x:si>
   <x:si>
-    <x:t>1.4 Click 'firefox.exe synergydms.…(5)' (NClick)</x:t>
+    <x:t>1.311 Click 'firefox.exe synergydms.…(5)' (NClick)</x:t>
   </x:si>
   <x:si>
     <x:t>Key modifiers = None</x:t>
@@ -201,54 +210,416 @@
     <x:t>Healing Agent mode = SameAsCard</x:t>
   </x:si>
   <x:si>
-    <x:t>1.36 CV Screen Scope 'BODY' (CVScope)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.38 UiPathScreenOCR (UiPathScreenOCR)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.37 Do (Sequence)</x:t>
+    <x:t>1.262 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.300 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.263 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.289 CV Click - Text (CvClickWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Descriptor = "Target: Text 'Workspace Name' (74,100,116,18)" +
 "Anchor: Text 'Document Type' (67,150,120,20)"</x:t>
   </x:si>
   <x:si>
-    <x:t>1.6 CV Type Into - Text (CvTypeIntoWithDescriptor)</x:t>
+    <x:t>1.275 CV Type Into - Text (CvTypeIntoWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Text = "hashim"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.264 CV Click - 'Inputbox' (CvClickWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Descriptor = "Target: InputBox (59,177,546,48)" +
 "Anchor: Text 'Document Type' (67,150,120,20)"</x:t>
   </x:si>
   <x:si>
+    <x:t>1.227 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.251 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.228 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.240 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Descriptor = "Target: Text 'General Document' (81,118,143,17)"</x:t>
   </x:si>
   <x:si>
+    <x:t>1.229 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Descriptor = "Target: Text 'OK' (291,347,23,17)"</x:t>
   </x:si>
   <x:si>
+    <x:t>1.203 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.216 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.204 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.205 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Descriptor = "Target: Text 'Save' (433,41,33,16)"</x:t>
   </x:si>
   <x:si>
-    <x:t>1.4 Click 'firefox.exe synergydms.…(6)' (NClick)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Click type = UiPath.UIAutomationNext.Enums.NClickType.Double</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.4 Click 'firefox.exe synergydms.…(7)' (NClick)</x:t>
+    <x:t>1.201 Delay (Delay)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duration = 00:00:05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.177 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.190 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.178 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.179 CV Click - 'Icon' (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Icon (62,38,58,51)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClickType = CLICK_DOUBLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.167 Click 'firefox.exe synergydms.…(7)' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.118 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.156 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.119 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.145 CV Click - Text (CvClickWithDescriptor)</x:t>
   </x:si>
   <x:si>
     <x:t>Descriptor = "Target: Text 'Enter Folder Name' (55,90,122,15)"</x:t>
   </x:si>
   <x:si>
+    <x:t>1.131 CV Type Into - Text (CvTypeIntoWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Text = "Hashim automation test"</x:t>
   </x:si>
   <x:si>
+    <x:t>1.120 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Descriptor = "Target: Text 'Save' (436,188,34,16)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.74 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.107 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.75 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.96 CV Click - 'Icon' (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Icon (56,34,63,48)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.86 Click 'firefox.exe synergydms.…(8)' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.76 Click 'firefox.exe synergydms.…(9)' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.72 Delay (Delay)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.48 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.61 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.49 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.50 CV Click - 'Button' (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Button (7,14,133,150)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.38 Click 'firefox.exe synergydms.…(10)' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.27 Click 'Edit' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input mode = SameAsCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Window selector (Application instance) = &lt;wnd app='firefox.exe' appid='Mozilla.Firefox_n80bbvh6b1yt2!App' title='File Upload' /&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strict selector = &lt;wnd ctrlid='1148' /&gt;&lt;wnd ctrlid='1148' /&gt;&lt;wnd ctrlid='1148' /&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Targeting methods = Selector, Image</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.15 Type Into 'Edit(1)' (NTypeInto)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text = C:\Users\xtpl\Downloads\Pension Operations TOBE- V5.0-OPS_NDCPS.docx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click before typing = Single</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Empty field = SingleLine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type by clipboard = Never</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Verify execution</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Verify element = Appears</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4 Click '&amp;Open' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strict selector = &lt;wnd ctrlid='1' title='&amp;amp;Open' /&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.76 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Document Name' (19,41,88,11)" +
+"Anchor: Text 'Document Name*' (13,3,111,14)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Type Into - Text (CvTypeIntoWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text = "Pension document"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.110 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.112 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.111 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Description' (19,36,60,13)" +
+"Anchor: Text 'Description' (13,3,71,15)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text = "this is the tobe pension document"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Document Name' (13,40,88,11)" +
+"Anchor: Text 'Document Name' (7,7,103,12)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text = "pension document"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.388 Click 'Select/Dropdown' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Responsive websites = True</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anchor 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Targeting methods = CV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CV Control type = Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CV Text = Select/Dropdown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsLinkedToReadOnlyObjectRepository = False</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CV Control type = InputBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.388 Click 'General Document' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4 Mouse Scroll 'firefox.exe synergydms.…(14)' (NMouseScroll)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direction = Down</x:t>
+  </x:si>
+  <x:si>
+    <x:t># of scrolls = 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Searched element</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4 CV Screen Scope 'firefox.exe  synergydms...' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Click - 'Inputbox' (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: InputBox (6,31,273,40)" +
+"Anchor: Text 'Approval Type' (11,10,89,17)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 Click 'firefox.exe synergydms.…(12)' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Publish' (287,148,41,13)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.24 Delay (Delay)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duration = 00:00:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Click - 'Checkbox' (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: CheckBox (21,19,17,16)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Click - 'trash can icon' (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Icon (158,11,17,21)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Confirm' (243,114,54,17)" +
+"Anchor: Button (221,106,100,35)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'hashim' (68,13,46,14)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4 Delay (Delay)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: CheckBox (36,24,17,16)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Icon (147,19,17,22)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.100 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.113 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.101 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.102 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Confirm' (249,121,54,17)" +
+"Anchor: Button (227,113,100,34)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Home' (14,17,34,11)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.8 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.7 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: CheckBox (40,14,18,16)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Icon (94,10,18,22)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Confirm' (249,121,54,17)" +
+"Anchor: Button (227,113,100,34)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 CV Screen Scope 'firefox.exe  synergydms...' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'S' (42,16,11,13)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.6 Click 'firefox.exe synergydms.…(13)' (NClick)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.10 CV Screen Scope 'BODY' (CVScope)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.12 UiPathScreenOCR (UiPathScreenOCR)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.11 Do (Sequence)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.10 CV Click - Text (CvClickWithDescriptor)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Descriptor = "Target: Text 'Logout' (171,135,48,20)" +
+"Anchor: Button (143,117,104,55)"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.4 Message Box (MessageBox)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content = "The automation ran successfully all operation to delete and creation done "</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AutomaticallyCloseAfter = 00:00:00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -603,1461 +974,5246 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L291"/>
+  <x:dimension ref="A1:M1048"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:12">
+    <x:row r="1" spans="1:13">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:12">
+    <x:row r="2" spans="1:13">
       <x:c r="B2" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:12">
+    <x:row r="3" spans="1:13">
       <x:c r="B3" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:12">
+    <x:row r="4" spans="1:13">
       <x:c r="C4" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:12">
+    <x:row r="5" spans="1:13">
       <x:c r="D5" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:12">
+    <x:row r="6" spans="1:13">
       <x:c r="E6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:12">
+    <x:row r="7" spans="1:13">
       <x:c r="E7" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:12">
+    <x:row r="8" spans="1:13">
       <x:c r="D8" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:12">
+    <x:row r="9" spans="1:13">
       <x:c r="D9" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:12">
+    <x:row r="10" spans="1:13">
       <x:c r="D10" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:12">
+    <x:row r="11" spans="1:13">
       <x:c r="D11" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:12">
+    <x:row r="12" spans="1:13">
       <x:c r="D12" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:12">
+    <x:row r="13" spans="1:13">
       <x:c r="D13" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:12">
+    <x:row r="14" spans="1:13">
       <x:c r="D14" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:12">
+    <x:row r="15" spans="1:13">
       <x:c r="E15" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:12">
+    <x:row r="16" spans="1:13">
       <x:c r="F16" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:12">
+    <x:row r="17" spans="1:13">
       <x:c r="F17" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:12">
+    <x:row r="18" spans="1:13">
       <x:c r="G18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:12">
+    <x:row r="19" spans="1:13">
       <x:c r="H19" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:12">
+    <x:row r="20" spans="1:13">
       <x:c r="I20" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:12">
+    <x:row r="21" spans="1:13">
       <x:c r="I21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:12">
+    <x:row r="22" spans="1:13">
       <x:c r="I22" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:12">
+    <x:row r="23" spans="1:13">
       <x:c r="H23" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:12">
+    <x:row r="24" spans="1:13">
       <x:c r="H24" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:12">
+    <x:row r="25" spans="1:13">
       <x:c r="H25" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:12">
+    <x:row r="26" spans="1:13">
       <x:c r="I26" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:12">
+    <x:row r="27" spans="1:13">
       <x:c r="J27" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:12">
+    <x:row r="28" spans="1:13">
       <x:c r="J28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:12">
+    <x:row r="29" spans="1:13">
       <x:c r="J29" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:12">
+    <x:row r="30" spans="1:13">
       <x:c r="J30" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:12">
+    <x:row r="31" spans="1:13">
       <x:c r="J31" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:12">
+    <x:row r="32" spans="1:13">
       <x:c r="H32" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:12">
+    <x:row r="33" spans="1:13">
       <x:c r="I33" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:12">
+    <x:row r="34" spans="1:13">
       <x:c r="J34" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:12">
+    <x:row r="35" spans="1:13">
       <x:c r="J35" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:12">
+    <x:row r="36" spans="1:13">
       <x:c r="K36" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:12">
-      <x:c r="L37" s="1" t="s">
+    <x:row r="37" spans="1:13">
+      <x:c r="L37" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:12">
+    <x:row r="38" spans="1:13">
       <x:c r="L38" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:12">
+    <x:row r="39" spans="1:13">
       <x:c r="L39" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:12">
+    <x:row r="40" spans="1:13">
       <x:c r="L40" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:12">
+    <x:row r="41" spans="1:13">
       <x:c r="L41" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:12">
+    <x:row r="42" spans="1:13">
       <x:c r="L42" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:12">
+    <x:row r="43" spans="1:13">
       <x:c r="L43" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:12">
+    <x:row r="44" spans="1:13">
       <x:c r="K44" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:12">
+    <x:row r="45" spans="1:13">
       <x:c r="L45" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:12">
-      <x:c r="L46" s="1" t="s">
+    <x:row r="46" spans="1:13">
+      <x:c r="L46" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:12">
+    <x:row r="47" spans="1:13">
       <x:c r="L47" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:12">
+    <x:row r="48" spans="1:13">
       <x:c r="L48" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:12">
+    <x:row r="49" spans="1:13">
       <x:c r="L49" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:12">
+    <x:row r="50" spans="1:13">
       <x:c r="L50" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:12">
+    <x:row r="51" spans="1:13">
       <x:c r="L51" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:12">
+    <x:row r="52" spans="1:13">
       <x:c r="L52" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:12">
+    <x:row r="53" spans="1:13">
       <x:c r="K53" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:12">
-      <x:c r="L54" s="1" t="s">
+    <x:row r="54" spans="1:13">
+      <x:c r="L54" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:12">
+    <x:row r="55" spans="1:13">
       <x:c r="L55" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:12">
+    <x:row r="56" spans="1:13">
       <x:c r="L56" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:12">
+    <x:row r="57" spans="1:13">
       <x:c r="L57" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:12">
+    <x:row r="58" spans="1:13">
       <x:c r="L58" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:12">
+    <x:row r="59" spans="1:13">
       <x:c r="L59" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:12">
+    <x:row r="60" spans="1:13">
       <x:c r="L60" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:12">
+    <x:row r="61" spans="1:13">
       <x:c r="G61" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:12">
+    <x:row r="62" spans="1:13">
       <x:c r="H62" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:12">
+    <x:row r="63" spans="1:13">
       <x:c r="H63" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:12">
+    <x:row r="64" spans="1:13">
       <x:c r="G64" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:12">
+    <x:row r="65" spans="1:13">
       <x:c r="H65" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:12">
+    <x:row r="66" spans="1:13">
       <x:c r="I66" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" spans="1:12">
+    <x:row r="67" spans="1:13">
       <x:c r="I67" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:12">
+    <x:row r="68" spans="1:13">
       <x:c r="H68" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" spans="1:12">
+    <x:row r="69" spans="1:13">
       <x:c r="H69" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:12">
+    <x:row r="70" spans="1:13">
       <x:c r="H70" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:12">
+    <x:row r="71" spans="1:13">
       <x:c r="I71" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:12">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:13">
       <x:c r="J72" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:12">
+    <x:row r="73" spans="1:13">
       <x:c r="J73" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:12">
+    <x:row r="74" spans="1:13">
       <x:c r="J74" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:12">
+    <x:row r="75" spans="1:13">
       <x:c r="J75" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" spans="1:12">
+    <x:row r="76" spans="1:13">
       <x:c r="J76" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" spans="1:12">
+    <x:row r="77" spans="1:13">
       <x:c r="H77" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" spans="1:12">
+    <x:row r="78" spans="1:13">
       <x:c r="I78" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:12">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:13">
       <x:c r="J79" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" spans="1:12">
+    <x:row r="80" spans="1:13">
       <x:c r="J80" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" spans="1:12">
+    <x:row r="81" spans="1:13">
       <x:c r="K81" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:12">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:13">
       <x:c r="L82" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:12">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:13">
       <x:c r="L83" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" spans="1:12">
+    <x:row r="84" spans="1:13">
       <x:c r="L84" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" spans="1:12">
+    <x:row r="85" spans="1:13">
       <x:c r="L85" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:12">
+    <x:row r="86" spans="1:13">
       <x:c r="L86" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:12">
+    <x:row r="87" spans="1:13">
       <x:c r="L87" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" spans="1:12">
+    <x:row r="88" spans="1:13">
       <x:c r="L88" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" spans="1:12">
+    <x:row r="89" spans="1:13">
       <x:c r="K89" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:12">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:13">
       <x:c r="L90" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:12">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:13">
       <x:c r="L91" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" spans="1:12">
+    <x:row r="92" spans="1:13">
       <x:c r="G92" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:12">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:13">
       <x:c r="H93" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:12">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:13">
       <x:c r="H94" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:12">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:13">
       <x:c r="H95" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:12">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:13">
       <x:c r="H96" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:12">
+    <x:row r="97" spans="1:13">
       <x:c r="H97" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:12">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:13">
       <x:c r="H98" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:12">
+    <x:row r="99" spans="1:13">
       <x:c r="I99" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:12">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:13">
       <x:c r="I100" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:12">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:13">
       <x:c r="I101" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:12">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:13">
       <x:c r="I102" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:12">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:13">
       <x:c r="I103" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:12">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:13">
       <x:c r="I104" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:12">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:13">
       <x:c r="I105" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:12">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:13">
       <x:c r="I106" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:12">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:13">
       <x:c r="H107" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:12">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:13">
       <x:c r="H108" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:12">
+    <x:row r="109" spans="1:13">
       <x:c r="G109" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:12">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:13">
       <x:c r="H110" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" spans="1:12">
+    <x:row r="111" spans="1:13">
       <x:c r="I111" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" spans="1:12">
+    <x:row r="112" spans="1:13">
       <x:c r="I112" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" spans="1:12">
+    <x:row r="113" spans="1:13">
       <x:c r="I113" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" spans="1:12">
+    <x:row r="114" spans="1:13">
       <x:c r="H114" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" spans="1:12">
+    <x:row r="115" spans="1:13">
       <x:c r="H115" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" spans="1:12">
+    <x:row r="116" spans="1:13">
       <x:c r="H116" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" spans="1:12">
+    <x:row r="117" spans="1:13">
       <x:c r="I117" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:12">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:13">
       <x:c r="J118" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" spans="1:12">
+    <x:row r="119" spans="1:13">
       <x:c r="J119" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" spans="1:12">
+    <x:row r="120" spans="1:13">
       <x:c r="J120" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" spans="1:12">
+    <x:row r="121" spans="1:13">
       <x:c r="J121" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" spans="1:12">
+    <x:row r="122" spans="1:13">
       <x:c r="J122" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" spans="1:12">
+    <x:row r="123" spans="1:13">
       <x:c r="H123" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" spans="1:12">
+    <x:row r="124" spans="1:13">
       <x:c r="I124" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:12">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:13">
       <x:c r="J125" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" spans="1:12">
+    <x:row r="126" spans="1:13">
       <x:c r="J126" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" spans="1:12">
+    <x:row r="127" spans="1:13">
       <x:c r="K127" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:12">
-      <x:c r="L128" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:12">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:13">
+      <x:c r="L128" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:13">
       <x:c r="L129" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" spans="1:12">
+    <x:row r="130" spans="1:13">
       <x:c r="L130" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" spans="1:12">
+    <x:row r="131" spans="1:13">
       <x:c r="L131" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" spans="1:12">
+    <x:row r="132" spans="1:13">
       <x:c r="L132" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" spans="1:12">
+    <x:row r="133" spans="1:13">
       <x:c r="L133" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" spans="1:12">
+    <x:row r="134" spans="1:13">
       <x:c r="L134" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" spans="1:12">
+    <x:row r="135" spans="1:13">
       <x:c r="K135" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:12">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:13">
       <x:c r="L136" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:12">
-      <x:c r="L137" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:12">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:13">
+      <x:c r="L137" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:13">
       <x:c r="L138" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" spans="1:12">
+    <x:row r="139" spans="1:13">
       <x:c r="L139" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" spans="1:12">
+    <x:row r="140" spans="1:13">
       <x:c r="L140" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" spans="1:12">
+    <x:row r="141" spans="1:13">
       <x:c r="L141" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" spans="1:12">
+    <x:row r="142" spans="1:13">
       <x:c r="L142" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" spans="1:12">
+    <x:row r="143" spans="1:13">
       <x:c r="L143" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" spans="1:12">
+    <x:row r="144" spans="1:13">
       <x:c r="K144" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:12">
-      <x:c r="L145" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:12">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:13">
+      <x:c r="L145" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:13">
       <x:c r="L146" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" spans="1:12">
+    <x:row r="147" spans="1:13">
       <x:c r="L147" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" spans="1:12">
+    <x:row r="148" spans="1:13">
       <x:c r="L148" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" spans="1:12">
+    <x:row r="149" spans="1:13">
       <x:c r="L149" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" spans="1:12">
+    <x:row r="150" spans="1:13">
       <x:c r="L150" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" spans="1:12">
+    <x:row r="151" spans="1:13">
       <x:c r="L151" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" spans="1:12">
+    <x:row r="152" spans="1:13">
       <x:c r="G152" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:12">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:13">
       <x:c r="H153" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" spans="1:12">
+    <x:row r="154" spans="1:13">
       <x:c r="I154" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" spans="1:12">
+    <x:row r="155" spans="1:13">
       <x:c r="I155" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" spans="1:12">
+    <x:row r="156" spans="1:13">
       <x:c r="I156" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" spans="1:12">
+    <x:row r="157" spans="1:13">
       <x:c r="H157" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" spans="1:12">
+    <x:row r="158" spans="1:13">
       <x:c r="H158" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" spans="1:12">
+    <x:row r="159" spans="1:13">
       <x:c r="H159" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" spans="1:12">
+    <x:row r="160" spans="1:13">
       <x:c r="I160" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:12">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:13">
       <x:c r="J161" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" spans="1:12">
+    <x:row r="162" spans="1:13">
       <x:c r="J162" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" spans="1:12">
+    <x:row r="163" spans="1:13">
       <x:c r="J163" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" spans="1:12">
+    <x:row r="164" spans="1:13">
       <x:c r="J164" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" spans="1:12">
+    <x:row r="165" spans="1:13">
       <x:c r="J165" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" spans="1:12">
+    <x:row r="166" spans="1:13">
       <x:c r="H166" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" spans="1:12">
+    <x:row r="167" spans="1:13">
       <x:c r="I167" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:12">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:13">
       <x:c r="J168" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" spans="1:12">
+    <x:row r="169" spans="1:13">
       <x:c r="J169" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" spans="1:12">
+    <x:row r="170" spans="1:13">
       <x:c r="K170" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:12">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:13">
       <x:c r="L171" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:12">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:13">
       <x:c r="L172" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" spans="1:12">
+    <x:row r="173" spans="1:13">
       <x:c r="L173" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" spans="1:12">
+    <x:row r="174" spans="1:13">
       <x:c r="L174" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" spans="1:12">
+    <x:row r="175" spans="1:13">
       <x:c r="L175" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" spans="1:12">
+    <x:row r="176" spans="1:13">
       <x:c r="L176" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" spans="1:12">
+    <x:row r="177" spans="1:13">
       <x:c r="L177" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" spans="1:12">
+    <x:row r="178" spans="1:13">
       <x:c r="K178" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:12">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:13">
       <x:c r="L179" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:12">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:13">
       <x:c r="L180" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" spans="1:12">
+    <x:row r="181" spans="1:13">
       <x:c r="L181" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" spans="1:12">
+    <x:row r="182" spans="1:13">
       <x:c r="L182" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" spans="1:12">
+    <x:row r="183" spans="1:13">
       <x:c r="L183" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" spans="1:12">
+    <x:row r="184" spans="1:13">
       <x:c r="L184" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" spans="1:12">
+    <x:row r="185" spans="1:13">
       <x:c r="L185" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" spans="1:12">
+    <x:row r="186" spans="1:13">
       <x:c r="G186" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:12">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:13">
       <x:c r="H187" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" spans="1:12">
+    <x:row r="188" spans="1:13">
       <x:c r="I188" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" spans="1:12">
+    <x:row r="189" spans="1:13">
       <x:c r="I189" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" spans="1:12">
+    <x:row r="190" spans="1:13">
       <x:c r="I190" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" spans="1:12">
+    <x:row r="191" spans="1:13">
       <x:c r="H191" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" spans="1:12">
+    <x:row r="192" spans="1:13">
       <x:c r="H192" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" spans="1:12">
+    <x:row r="193" spans="1:13">
       <x:c r="H193" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" spans="1:12">
+    <x:row r="194" spans="1:13">
       <x:c r="I194" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:12">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:13">
       <x:c r="J195" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" spans="1:12">
+    <x:row r="196" spans="1:13">
       <x:c r="J196" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" spans="1:12">
+    <x:row r="197" spans="1:13">
       <x:c r="J197" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" spans="1:12">
+    <x:row r="198" spans="1:13">
       <x:c r="J198" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" spans="1:12">
+    <x:row r="199" spans="1:13">
       <x:c r="J199" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" spans="1:12">
+    <x:row r="200" spans="1:13">
       <x:c r="H200" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" spans="1:12">
+    <x:row r="201" spans="1:13">
       <x:c r="I201" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:12">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:13">
       <x:c r="J202" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" spans="1:12">
+    <x:row r="203" spans="1:13">
       <x:c r="J203" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" spans="1:12">
+    <x:row r="204" spans="1:13">
       <x:c r="K204" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:12">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:13">
       <x:c r="L205" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:12">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:13">
       <x:c r="L206" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" spans="1:12">
+    <x:row r="207" spans="1:13">
       <x:c r="L207" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" spans="1:12">
+    <x:row r="208" spans="1:13">
       <x:c r="L208" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" spans="1:12">
+    <x:row r="209" spans="1:13">
       <x:c r="L209" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" spans="1:12">
+    <x:row r="210" spans="1:13">
       <x:c r="L210" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" spans="1:12">
+    <x:row r="211" spans="1:13">
       <x:c r="L211" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" spans="1:12">
+    <x:row r="212" spans="1:13">
       <x:c r="G212" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" spans="1:12">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:13">
       <x:c r="H213" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" spans="1:12">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:13">
       <x:c r="H214" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" spans="1:12">
-      <x:c r="H215" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" spans="1:12">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:13">
+      <x:c r="G215" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:13">
       <x:c r="H216" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:13">
+      <x:c r="I217" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:13">
+      <x:c r="I218" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:13">
+      <x:c r="I219" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:13">
+      <x:c r="H220" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:13">
+      <x:c r="H221" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:13">
+      <x:c r="H222" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:13">
+      <x:c r="I223" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:13">
+      <x:c r="J224" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:13">
+      <x:c r="J225" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:13">
+      <x:c r="J226" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:13">
+      <x:c r="J227" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:13">
+      <x:c r="J228" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:13">
+      <x:c r="H229" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:13">
+      <x:c r="I230" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:13">
+      <x:c r="J231" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:13">
+      <x:c r="J232" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:13">
+      <x:c r="K233" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:13">
+      <x:c r="L234" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:13">
+      <x:c r="L235" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:13">
+      <x:c r="L236" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:13">
+      <x:c r="L237" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:13">
+      <x:c r="L238" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:13">
+      <x:c r="L239" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:13">
+      <x:c r="L240" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:13">
+      <x:c r="G241" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:13">
+      <x:c r="H242" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:13">
+      <x:c r="H243" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:13">
+      <x:c r="H244" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:13">
+      <x:c r="H245" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" spans="1:12">
-      <x:c r="H217" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" spans="1:12">
-      <x:c r="H218" s="0" t="s">
+    <x:row r="246" spans="1:13">
+      <x:c r="H246" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:13">
+      <x:c r="H247" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" spans="1:12">
-      <x:c r="I219" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" spans="1:12">
-      <x:c r="I220" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" spans="1:12">
-      <x:c r="I221" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" spans="1:12">
-      <x:c r="I222" s="0" t="s">
+    <x:row r="248" spans="1:13">
+      <x:c r="I248" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="223" spans="1:12">
-      <x:c r="I223" s="0" t="s">
+    <x:row r="249" spans="1:13">
+      <x:c r="I249" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" spans="1:12">
-      <x:c r="I224" s="0" t="s">
+    <x:row r="250" spans="1:13">
+      <x:c r="I250" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="225" spans="1:12">
-      <x:c r="I225" s="0" t="s">
+    <x:row r="251" spans="1:13">
+      <x:c r="I251" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" spans="1:12">
-      <x:c r="I226" s="0" t="s">
+    <x:row r="252" spans="1:13">
+      <x:c r="I252" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" spans="1:12">
-      <x:c r="H227" s="0" t="s">
+    <x:row r="253" spans="1:13">
+      <x:c r="I253" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="228" spans="1:12">
-      <x:c r="H228" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229" spans="1:12">
-      <x:c r="G229" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="230" spans="1:12">
-      <x:c r="H230" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="231" spans="1:12">
-      <x:c r="H231" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="232" spans="1:12">
-      <x:c r="G232" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="233" spans="1:12">
-      <x:c r="H233" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="234" spans="1:12">
-      <x:c r="H234" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="235" spans="1:12">
-      <x:c r="H235" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="236" spans="1:12">
-      <x:c r="H236" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="237" spans="1:12">
-      <x:c r="H237" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="238" spans="1:12">
-      <x:c r="H238" s="0" t="s">
+    <x:row r="254" spans="1:13">
+      <x:c r="I254" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:13">
+      <x:c r="I255" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:13">
+      <x:c r="H256" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:13">
+      <x:c r="H257" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:13">
+      <x:c r="G258" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:13">
+      <x:c r="H259" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" spans="1:12">
-      <x:c r="I239" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="240" spans="1:12">
-      <x:c r="I240" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="241" spans="1:12">
-      <x:c r="I241" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="242" spans="1:12">
-      <x:c r="I242" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="243" spans="1:12">
-      <x:c r="I243" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="244" spans="1:12">
-      <x:c r="I244" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="245" spans="1:12">
-      <x:c r="I245" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="246" spans="1:12">
-      <x:c r="I246" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="247" spans="1:12">
-      <x:c r="H247" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="248" spans="1:12">
-      <x:c r="H248" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="249" spans="1:12">
-      <x:c r="G249" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="250" spans="1:12">
-      <x:c r="H250" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="251" spans="1:12">
-      <x:c r="I251" s="0" t="s">
+    <x:row r="260" spans="1:13">
+      <x:c r="I260" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" spans="1:12">
-      <x:c r="I252" s="0" t="s">
+    <x:row r="261" spans="1:13">
+      <x:c r="I261" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" spans="1:12">
-      <x:c r="I253" s="0" t="s">
+    <x:row r="262" spans="1:13">
+      <x:c r="I262" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" spans="1:12">
-      <x:c r="H254" s="0" t="s">
+    <x:row r="263" spans="1:13">
+      <x:c r="H263" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" spans="1:12">
-      <x:c r="H255" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="256" spans="1:12">
-      <x:c r="H256" s="0" t="s">
+    <x:row r="264" spans="1:13">
+      <x:c r="H264" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:13">
+      <x:c r="H265" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" spans="1:12">
-      <x:c r="I257" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="258" spans="1:12">
-      <x:c r="J258" s="0" t="s">
+    <x:row r="266" spans="1:13">
+      <x:c r="I266" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:13">
+      <x:c r="J267" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" spans="1:12">
-      <x:c r="J259" s="0" t="s">
+    <x:row r="268" spans="1:13">
+      <x:c r="J268" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="260" spans="1:12">
-      <x:c r="J260" s="0" t="s">
+    <x:row r="269" spans="1:13">
+      <x:c r="J269" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" spans="1:12">
-      <x:c r="J261" s="0" t="s">
+    <x:row r="270" spans="1:13">
+      <x:c r="J270" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="262" spans="1:12">
-      <x:c r="J262" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="263" spans="1:12">
-      <x:c r="H263" s="0" t="s">
+    <x:row r="271" spans="1:13">
+      <x:c r="J271" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:13">
+      <x:c r="H272" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="264" spans="1:12">
-      <x:c r="I264" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="265" spans="1:12">
-      <x:c r="J265" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="266" spans="1:12">
-      <x:c r="J266" s="0" t="s">
+    <x:row r="273" spans="1:13">
+      <x:c r="I273" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:13">
+      <x:c r="J274" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:13">
+      <x:c r="J275" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="267" spans="1:12">
-      <x:c r="K267" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="268" spans="1:12">
-      <x:c r="L268" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="269" spans="1:12">
-      <x:c r="L269" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="270" spans="1:12">
-      <x:c r="L270" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="271" spans="1:12">
-      <x:c r="L271" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272" spans="1:12">
-      <x:c r="L272" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="273" spans="1:12">
-      <x:c r="L273" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="274" spans="1:12">
-      <x:c r="L274" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="275" spans="1:12">
-      <x:c r="K275" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="276" spans="1:12">
-      <x:c r="L276" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="277" spans="1:12">
+    <x:row r="276" spans="1:13">
+      <x:c r="K276" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:13">
       <x:c r="L277" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="278" spans="1:12">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:13">
       <x:c r="L278" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="279" spans="1:12">
+    <x:row r="279" spans="1:13">
       <x:c r="L279" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="280" spans="1:12">
+    <x:row r="280" spans="1:13">
       <x:c r="L280" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:13">
+      <x:c r="L281" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:13">
+      <x:c r="L282" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:13">
+      <x:c r="L283" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:13">
+      <x:c r="K284" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:13">
+      <x:c r="L285" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:13">
+      <x:c r="L286" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:13">
+      <x:c r="L287" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:13">
+      <x:c r="L288" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:13">
+      <x:c r="L289" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="281" spans="1:12">
-      <x:c r="L281" s="0" t="s">
+    <x:row r="290" spans="1:13">
+      <x:c r="L290" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="282" spans="1:12">
-      <x:c r="L282" s="0" t="s">
+    <x:row r="291" spans="1:13">
+      <x:c r="L291" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="283" spans="1:12">
-      <x:c r="L283" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="284" spans="1:12">
-      <x:c r="K284" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="285" spans="1:12">
-      <x:c r="L285" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="286" spans="1:12">
-      <x:c r="L286" s="0" t="s">
+    <x:row r="292" spans="1:13">
+      <x:c r="L292" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:13">
+      <x:c r="K293" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:13">
+      <x:c r="L294" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:13">
+      <x:c r="L295" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="287" spans="1:12">
-      <x:c r="L287" s="0" t="s">
+    <x:row r="296" spans="1:13">
+      <x:c r="L296" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="288" spans="1:12">
-      <x:c r="L288" s="0" t="s">
+    <x:row r="297" spans="1:13">
+      <x:c r="L297" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="289" spans="1:12">
-      <x:c r="L289" s="0" t="s">
+    <x:row r="298" spans="1:13">
+      <x:c r="L298" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="290" spans="1:12">
-      <x:c r="L290" s="0" t="s">
+    <x:row r="299" spans="1:13">
+      <x:c r="L299" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="291" spans="1:12">
-      <x:c r="L291" s="0" t="s">
+    <x:row r="300" spans="1:13">
+      <x:c r="L300" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:13">
+      <x:c r="G301" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:13">
+      <x:c r="H302" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:13">
+      <x:c r="I303" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:13">
+      <x:c r="I304" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:13">
+      <x:c r="I305" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:13">
+      <x:c r="H306" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:13">
+      <x:c r="H307" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:13">
+      <x:c r="H308" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:13">
+      <x:c r="I309" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:13">
+      <x:c r="J310" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:13">
+      <x:c r="J311" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:13">
+      <x:c r="J312" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:13">
+      <x:c r="J313" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:13">
+      <x:c r="J314" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:13">
+      <x:c r="H315" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:13">
+      <x:c r="I316" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:13">
+      <x:c r="J317" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:13">
+      <x:c r="J318" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:13">
+      <x:c r="K319" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:13">
+      <x:c r="L320" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:13">
+      <x:c r="L321" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:13">
+      <x:c r="L322" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:13">
+      <x:c r="L323" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:13">
+      <x:c r="L324" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:13">
+      <x:c r="L325" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:13">
+      <x:c r="L326" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:13">
+      <x:c r="K327" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:13">
+      <x:c r="L328" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:13">
+      <x:c r="L329" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:13">
+      <x:c r="L330" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:13">
+      <x:c r="L331" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:13">
+      <x:c r="L332" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:13">
+      <x:c r="L333" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:13">
+      <x:c r="M334" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:13">
+      <x:c r="M335" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:13">
+      <x:c r="M336" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:13">
+      <x:c r="M337" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:13">
+      <x:c r="M338" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:13">
+      <x:c r="M339" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:13">
+      <x:c r="M340" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:13">
+      <x:c r="M341" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:13">
+      <x:c r="L342" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:13">
+      <x:c r="L343" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:13">
+      <x:c r="K344" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:13">
+      <x:c r="L345" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:13">
+      <x:c r="L346" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:13">
+      <x:c r="L347" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:13">
+      <x:c r="L348" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:13">
+      <x:c r="L349" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:13">
+      <x:c r="L350" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:13">
+      <x:c r="M351" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:13">
+      <x:c r="M352" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:13">
+      <x:c r="M353" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:13">
+      <x:c r="M354" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:13">
+      <x:c r="M355" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:13">
+      <x:c r="M356" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:13">
+      <x:c r="M357" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:13">
+      <x:c r="M358" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:13">
+      <x:c r="L359" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" spans="1:13">
+      <x:c r="L360" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" spans="1:13">
+      <x:c r="G361" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" spans="1:13">
+      <x:c r="H362" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" spans="1:13">
+      <x:c r="H363" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" spans="1:13">
+      <x:c r="G364" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" spans="1:13">
+      <x:c r="H365" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" spans="1:13">
+      <x:c r="I366" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" spans="1:13">
+      <x:c r="I367" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" spans="1:13">
+      <x:c r="I368" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" spans="1:13">
+      <x:c r="H369" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" spans="1:13">
+      <x:c r="H370" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" spans="1:13">
+      <x:c r="H371" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" spans="1:13">
+      <x:c r="I372" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" spans="1:13">
+      <x:c r="J373" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" spans="1:13">
+      <x:c r="J374" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" spans="1:13">
+      <x:c r="J375" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" spans="1:13">
+      <x:c r="J376" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:13">
+      <x:c r="J377" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:13">
+      <x:c r="H378" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:13">
+      <x:c r="I379" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:13">
+      <x:c r="J380" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:13">
+      <x:c r="J381" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:13">
+      <x:c r="K382" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:13">
+      <x:c r="L383" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:13">
+      <x:c r="L384" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:13">
+      <x:c r="L385" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:13">
+      <x:c r="L386" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:13">
+      <x:c r="L387" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:13">
+      <x:c r="L388" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:13">
+      <x:c r="L389" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:13">
+      <x:c r="G390" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:13">
+      <x:c r="H391" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:13">
+      <x:c r="H392" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:13">
+      <x:c r="H393" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:13">
+      <x:c r="H394" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:13">
+      <x:c r="H395" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:13">
+      <x:c r="H396" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:13">
+      <x:c r="I397" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:13">
+      <x:c r="I398" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:13">
+      <x:c r="I399" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:13">
+      <x:c r="I400" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:13">
+      <x:c r="I401" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:13">
+      <x:c r="I402" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:13">
+      <x:c r="I403" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:13">
+      <x:c r="I404" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:13">
+      <x:c r="H405" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:13">
+      <x:c r="H406" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:13">
+      <x:c r="G407" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:13">
+      <x:c r="H408" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:13">
+      <x:c r="H409" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:13">
+      <x:c r="H410" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:13">
+      <x:c r="H411" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:13">
+      <x:c r="H412" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:13">
+      <x:c r="H413" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:13">
+      <x:c r="I414" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:13">
+      <x:c r="I415" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:13">
+      <x:c r="I416" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:13">
+      <x:c r="I417" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:13">
+      <x:c r="I418" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:13">
+      <x:c r="I419" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:13">
+      <x:c r="I420" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:13">
+      <x:c r="I421" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:13">
+      <x:c r="I422" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:13">
+      <x:c r="H423" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:13">
+      <x:c r="H424" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:13">
+      <x:c r="G425" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:13">
+      <x:c r="H426" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:13">
+      <x:c r="H427" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:13">
+      <x:c r="H428" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:13">
+      <x:c r="H429" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:13">
+      <x:c r="H430" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:13">
+      <x:c r="H431" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:13">
+      <x:c r="I432" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:13">
+      <x:c r="H433" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:13">
+      <x:c r="H434" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:13">
+      <x:c r="I435" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:13">
+      <x:c r="I436" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:13">
+      <x:c r="I437" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:13">
+      <x:c r="I438" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:13">
+      <x:c r="I439" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:13">
+      <x:c r="I440" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:13">
+      <x:c r="I441" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:13">
+      <x:c r="I442" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:13">
+      <x:c r="I443" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:13">
+      <x:c r="H444" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:13">
+      <x:c r="H445" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:13">
+      <x:c r="G446" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:13">
+      <x:c r="H447" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:13">
+      <x:c r="H448" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:13">
+      <x:c r="H449" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:13">
+      <x:c r="H450" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:13">
+      <x:c r="H451" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:13">
+      <x:c r="H452" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:13">
+      <x:c r="I453" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:13">
+      <x:c r="I454" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:13">
+      <x:c r="I455" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:13">
+      <x:c r="I456" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:13">
+      <x:c r="I457" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:13">
+      <x:c r="I458" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:13">
+      <x:c r="I459" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:13">
+      <x:c r="I460" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:13">
+      <x:c r="I461" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:13">
+      <x:c r="H462" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:13">
+      <x:c r="H463" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:13">
+      <x:c r="G464" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:13">
+      <x:c r="H465" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:13">
+      <x:c r="I466" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:13">
+      <x:c r="I467" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:13">
+      <x:c r="I468" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:13">
+      <x:c r="H469" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:13">
+      <x:c r="H470" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:13">
+      <x:c r="H471" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" spans="1:13">
+      <x:c r="I472" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:13">
+      <x:c r="J473" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:13">
+      <x:c r="J474" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:13">
+      <x:c r="J475" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:13">
+      <x:c r="J476" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:13">
+      <x:c r="J477" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:13">
+      <x:c r="H478" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:13">
+      <x:c r="I479" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:13">
+      <x:c r="J480" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:13">
+      <x:c r="J481" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:13">
+      <x:c r="K482" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:13">
+      <x:c r="L483" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:13">
+      <x:c r="L484" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:13">
+      <x:c r="L485" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:13">
+      <x:c r="L486" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:13">
+      <x:c r="L487" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:13">
+      <x:c r="L488" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:13">
+      <x:c r="L489" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:13">
+      <x:c r="K490" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:13">
+      <x:c r="L491" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:13">
+      <x:c r="L492" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:13">
+      <x:c r="L493" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:13">
+      <x:c r="L494" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:13">
+      <x:c r="L495" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:13">
+      <x:c r="L496" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:13">
+      <x:c r="L497" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:13">
+      <x:c r="L498" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:13">
+      <x:c r="G499" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:13">
+      <x:c r="H500" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:13">
+      <x:c r="I501" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:13">
+      <x:c r="I502" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:13">
+      <x:c r="I503" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:13">
+      <x:c r="H504" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:13">
+      <x:c r="H505" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:13">
+      <x:c r="H506" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:13">
+      <x:c r="I507" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:13">
+      <x:c r="J508" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:13">
+      <x:c r="J509" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:13">
+      <x:c r="J510" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:13">
+      <x:c r="J511" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:13">
+      <x:c r="J512" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:13">
+      <x:c r="H513" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:13">
+      <x:c r="I514" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:13">
+      <x:c r="J515" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:13">
+      <x:c r="J516" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:13">
+      <x:c r="K517" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:13">
+      <x:c r="L518" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:13">
+      <x:c r="L519" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:13">
+      <x:c r="L520" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:13">
+      <x:c r="L521" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:13">
+      <x:c r="L522" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:13">
+      <x:c r="L523" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:13">
+      <x:c r="L524" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:13">
+      <x:c r="K525" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:13">
+      <x:c r="L526" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:13">
+      <x:c r="L527" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" spans="1:13">
+      <x:c r="L528" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:13">
+      <x:c r="L529" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:13">
+      <x:c r="L530" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:13">
+      <x:c r="L531" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:13">
+      <x:c r="L532" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:13">
+      <x:c r="L533" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:13">
+      <x:c r="G534" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:13">
+      <x:c r="H535" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:13">
+      <x:c r="I536" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:13">
+      <x:c r="I537" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:13">
+      <x:c r="I538" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:13">
+      <x:c r="H539" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:13">
+      <x:c r="H540" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:13">
+      <x:c r="H541" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:13">
+      <x:c r="I542" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:13">
+      <x:c r="J543" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:13">
+      <x:c r="J544" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:13">
+      <x:c r="J545" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:13">
+      <x:c r="J546" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:13">
+      <x:c r="J547" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:13">
+      <x:c r="H548" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:13">
+      <x:c r="I549" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:13">
+      <x:c r="J550" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:13">
+      <x:c r="J551" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:13">
+      <x:c r="K552" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:13">
+      <x:c r="L553" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:13">
+      <x:c r="L554" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:13">
+      <x:c r="L555" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:13">
+      <x:c r="L556" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:13">
+      <x:c r="L557" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:13">
+      <x:c r="L558" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:13">
+      <x:c r="L559" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:13">
+      <x:c r="K560" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:13">
+      <x:c r="L561" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:13">
+      <x:c r="L562" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:13">
+      <x:c r="L563" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:13">
+      <x:c r="L564" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:13">
+      <x:c r="L565" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:13">
+      <x:c r="L566" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:13">
+      <x:c r="L567" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:13">
+      <x:c r="L568" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:13">
+      <x:c r="G569" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:13">
+      <x:c r="H570" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:13">
+      <x:c r="H571" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:13">
+      <x:c r="H572" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:13">
+      <x:c r="H573" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" spans="1:13">
+      <x:c r="H574" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" spans="1:13">
+      <x:c r="H575" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" spans="1:13">
+      <x:c r="I576" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" spans="1:13">
+      <x:c r="I577" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" spans="1:13">
+      <x:c r="I578" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" spans="1:13">
+      <x:c r="I579" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" spans="1:13">
+      <x:c r="I580" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" spans="1:13">
+      <x:c r="J581" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" spans="1:13">
+      <x:c r="J582" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" spans="1:13">
+      <x:c r="J583" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" spans="1:13">
+      <x:c r="J584" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" spans="1:13">
+      <x:c r="J585" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" spans="1:13">
+      <x:c r="J586" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" spans="1:13">
+      <x:c r="I587" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" spans="1:13">
+      <x:c r="I588" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" spans="1:13">
+      <x:c r="I589" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" spans="1:13">
+      <x:c r="I590" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" spans="1:13">
+      <x:c r="H591" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" spans="1:13">
+      <x:c r="H592" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" spans="1:13">
+      <x:c r="G593" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" spans="1:13">
+      <x:c r="H594" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" spans="1:13">
+      <x:c r="H595" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" spans="1:13">
+      <x:c r="H596" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" spans="1:13">
+      <x:c r="H597" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" spans="1:13">
+      <x:c r="H598" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" spans="1:13">
+      <x:c r="H599" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" spans="1:13">
+      <x:c r="I600" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" spans="1:13">
+      <x:c r="I601" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" spans="1:13">
+      <x:c r="I602" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" spans="1:13">
+      <x:c r="I603" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" spans="1:13">
+      <x:c r="I604" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" spans="1:13">
+      <x:c r="I605" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" spans="1:13">
+      <x:c r="I606" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" spans="1:13">
+      <x:c r="I607" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" spans="1:13">
+      <x:c r="H608" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" spans="1:13">
+      <x:c r="H609" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" spans="1:13">
+      <x:c r="G610" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" spans="1:13">
+      <x:c r="H611" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" spans="1:13">
+      <x:c r="H612" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" spans="1:13">
+      <x:c r="H613" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" spans="1:13">
+      <x:c r="I614" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" spans="1:13">
+      <x:c r="J615" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" spans="1:13">
+      <x:c r="J616" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" spans="1:13">
+      <x:c r="J617" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" spans="1:13">
+      <x:c r="J618" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" spans="1:13">
+      <x:c r="J619" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" spans="1:13">
+      <x:c r="J620" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" spans="1:13">
+      <x:c r="J621" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" spans="1:13">
+      <x:c r="J622" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" spans="1:13">
+      <x:c r="H623" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" spans="1:13">
+      <x:c r="H624" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" spans="1:13">
+      <x:c r="I625" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" spans="1:13">
+      <x:c r="I626" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" spans="1:13">
+      <x:c r="I627" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" spans="1:13">
+      <x:c r="I628" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" spans="1:13">
+      <x:c r="I629" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" spans="1:13">
+      <x:c r="I630" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" spans="1:13">
+      <x:c r="I631" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" spans="1:13">
+      <x:c r="I632" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" spans="1:13">
+      <x:c r="H633" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" spans="1:13">
+      <x:c r="H634" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" spans="1:13">
+      <x:c r="G635" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" spans="1:13">
+      <x:c r="H636" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" spans="1:13">
+      <x:c r="I637" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" spans="1:13">
+      <x:c r="I638" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" spans="1:13">
+      <x:c r="H639" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" spans="1:13">
+      <x:c r="H640" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" spans="1:13">
+      <x:c r="H641" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" spans="1:13">
+      <x:c r="I642" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" spans="1:13">
+      <x:c r="J643" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" spans="1:13">
+      <x:c r="J644" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" spans="1:13">
+      <x:c r="J645" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" spans="1:13">
+      <x:c r="J646" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" spans="1:13">
+      <x:c r="J647" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" spans="1:13">
+      <x:c r="H648" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" spans="1:13">
+      <x:c r="I649" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" spans="1:13">
+      <x:c r="J650" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" spans="1:13">
+      <x:c r="J651" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" spans="1:13">
+      <x:c r="K652" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" spans="1:13">
+      <x:c r="L653" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" spans="1:13">
+      <x:c r="L654" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" spans="1:13">
+      <x:c r="L655" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" spans="1:13">
+      <x:c r="L656" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" spans="1:13">
+      <x:c r="L657" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" spans="1:13">
+      <x:c r="L658" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" spans="1:13">
+      <x:c r="L659" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" spans="1:13">
+      <x:c r="K660" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" spans="1:13">
+      <x:c r="L661" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662" spans="1:13">
+      <x:c r="L662" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" spans="1:13">
+      <x:c r="L663" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" spans="1:13">
+      <x:c r="L664" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" spans="1:13">
+      <x:c r="L665" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" spans="1:13">
+      <x:c r="L666" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" spans="1:13">
+      <x:c r="M667" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" spans="1:13">
+      <x:c r="M668" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" spans="1:13">
+      <x:c r="M669" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" spans="1:13">
+      <x:c r="M670" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" spans="1:13">
+      <x:c r="M671" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" spans="1:13">
+      <x:c r="M672" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" spans="1:13">
+      <x:c r="M673" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" spans="1:13">
+      <x:c r="M674" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" spans="1:13">
+      <x:c r="L675" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" spans="1:13">
+      <x:c r="L676" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" spans="1:13">
+      <x:c r="K677" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" spans="1:13">
+      <x:c r="L678" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" spans="1:13">
+      <x:c r="L679" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" spans="1:13">
+      <x:c r="L680" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" spans="1:13">
+      <x:c r="L681" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" spans="1:13">
+      <x:c r="L682" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" spans="1:13">
+      <x:c r="L683" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" spans="1:13">
+      <x:c r="L684" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" spans="1:13">
+      <x:c r="G685" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" spans="1:13">
+      <x:c r="H686" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" spans="1:13">
+      <x:c r="H687" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" spans="1:13">
+      <x:c r="G688" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" spans="1:13">
+      <x:c r="H689" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" spans="1:13">
+      <x:c r="I690" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" spans="1:13">
+      <x:c r="I691" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" spans="1:13">
+      <x:c r="I692" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" spans="1:13">
+      <x:c r="H693" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" spans="1:13">
+      <x:c r="H694" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" spans="1:13">
+      <x:c r="H695" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" spans="1:13">
+      <x:c r="I696" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" spans="1:13">
+      <x:c r="J697" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" spans="1:13">
+      <x:c r="J698" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" spans="1:13">
+      <x:c r="J699" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" spans="1:13">
+      <x:c r="J700" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" spans="1:13">
+      <x:c r="J701" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" spans="1:13">
+      <x:c r="H702" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" spans="1:13">
+      <x:c r="I703" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" spans="1:13">
+      <x:c r="J704" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705" spans="1:13">
+      <x:c r="J705" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" spans="1:13">
+      <x:c r="K706" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" spans="1:13">
+      <x:c r="L707" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708" spans="1:13">
+      <x:c r="L708" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709" spans="1:13">
+      <x:c r="L709" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710" spans="1:13">
+      <x:c r="L710" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" spans="1:13">
+      <x:c r="L711" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" spans="1:13">
+      <x:c r="L712" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" spans="1:13">
+      <x:c r="L713" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714" spans="1:13">
+      <x:c r="G714" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715" spans="1:13">
+      <x:c r="H715" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" spans="1:13">
+      <x:c r="I716" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717" spans="1:13">
+      <x:c r="I717" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718" spans="1:13">
+      <x:c r="I718" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719" spans="1:13">
+      <x:c r="H719" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="720" spans="1:13">
+      <x:c r="H720" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="721" spans="1:13">
+      <x:c r="H721" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722" spans="1:13">
+      <x:c r="I722" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723" spans="1:13">
+      <x:c r="J723" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724" spans="1:13">
+      <x:c r="J724" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725" spans="1:13">
+      <x:c r="J725" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726" spans="1:13">
+      <x:c r="J726" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727" spans="1:13">
+      <x:c r="J727" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728" spans="1:13">
+      <x:c r="H728" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729" spans="1:13">
+      <x:c r="I729" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730" spans="1:13">
+      <x:c r="J730" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731" spans="1:13">
+      <x:c r="J731" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="732" spans="1:13">
+      <x:c r="K732" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="733" spans="1:13">
+      <x:c r="L733" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734" spans="1:13">
+      <x:c r="L734" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="735" spans="1:13">
+      <x:c r="L735" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="736" spans="1:13">
+      <x:c r="L736" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="737" spans="1:13">
+      <x:c r="L737" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="738" spans="1:13">
+      <x:c r="L738" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="739" spans="1:13">
+      <x:c r="L739" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="740" spans="1:13">
+      <x:c r="G740" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="741" spans="1:13">
+      <x:c r="H741" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="742" spans="1:13">
+      <x:c r="I742" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743" spans="1:13">
+      <x:c r="I743" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744" spans="1:13">
+      <x:c r="I744" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745" spans="1:13">
+      <x:c r="H745" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746" spans="1:13">
+      <x:c r="H746" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="747" spans="1:13">
+      <x:c r="H747" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="748" spans="1:13">
+      <x:c r="I748" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="749" spans="1:13">
+      <x:c r="J749" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="750" spans="1:13">
+      <x:c r="J750" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="751" spans="1:13">
+      <x:c r="J751" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="752" spans="1:13">
+      <x:c r="J752" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="753" spans="1:13">
+      <x:c r="J753" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="754" spans="1:13">
+      <x:c r="H754" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755" spans="1:13">
+      <x:c r="I755" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756" spans="1:13">
+      <x:c r="J756" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" spans="1:13">
+      <x:c r="J757" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758" spans="1:13">
+      <x:c r="K758" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759" spans="1:13">
+      <x:c r="L759" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760" spans="1:13">
+      <x:c r="L760" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761" spans="1:13">
+      <x:c r="L761" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762" spans="1:13">
+      <x:c r="L762" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763" spans="1:13">
+      <x:c r="L763" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764" spans="1:13">
+      <x:c r="L764" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765" spans="1:13">
+      <x:c r="L765" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766" spans="1:13">
+      <x:c r="G766" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767" spans="1:13">
+      <x:c r="H767" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768" spans="1:13">
+      <x:c r="I768" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" spans="1:13">
+      <x:c r="I769" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" spans="1:13">
+      <x:c r="I770" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771" spans="1:13">
+      <x:c r="H771" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" spans="1:13">
+      <x:c r="H772" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" spans="1:13">
+      <x:c r="H773" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774" spans="1:13">
+      <x:c r="I774" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" spans="1:13">
+      <x:c r="J775" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" spans="1:13">
+      <x:c r="J776" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777" spans="1:13">
+      <x:c r="J777" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778" spans="1:13">
+      <x:c r="J778" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" spans="1:13">
+      <x:c r="J779" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" spans="1:13">
+      <x:c r="H780" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" spans="1:13">
+      <x:c r="I781" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" spans="1:13">
+      <x:c r="J782" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" spans="1:13">
+      <x:c r="J783" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" spans="1:13">
+      <x:c r="K784" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" spans="1:13">
+      <x:c r="L785" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" spans="1:13">
+      <x:c r="L786" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" spans="1:13">
+      <x:c r="L787" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788" spans="1:13">
+      <x:c r="L788" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" spans="1:13">
+      <x:c r="L789" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" spans="1:13">
+      <x:c r="L790" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" spans="1:13">
+      <x:c r="L791" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792" spans="1:13">
+      <x:c r="G792" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793" spans="1:13">
+      <x:c r="H793" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794" spans="1:13">
+      <x:c r="H794" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795" spans="1:13">
+      <x:c r="G795" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796" spans="1:13">
+      <x:c r="H796" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797" spans="1:13">
+      <x:c r="I797" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798" spans="1:13">
+      <x:c r="I798" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" spans="1:13">
+      <x:c r="I799" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" spans="1:13">
+      <x:c r="H800" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" spans="1:13">
+      <x:c r="H801" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" spans="1:13">
+      <x:c r="H802" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" spans="1:13">
+      <x:c r="I803" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804" spans="1:13">
+      <x:c r="J804" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805" spans="1:13">
+      <x:c r="J805" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806" spans="1:13">
+      <x:c r="J806" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807" spans="1:13">
+      <x:c r="J807" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808" spans="1:13">
+      <x:c r="J808" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809" spans="1:13">
+      <x:c r="H809" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810" spans="1:13">
+      <x:c r="I810" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811" spans="1:13">
+      <x:c r="J811" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812" spans="1:13">
+      <x:c r="J812" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813" spans="1:13">
+      <x:c r="K813" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814" spans="1:13">
+      <x:c r="L814" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815" spans="1:13">
+      <x:c r="L815" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816" spans="1:13">
+      <x:c r="L816" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817" spans="1:13">
+      <x:c r="L817" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818" spans="1:13">
+      <x:c r="L818" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819" spans="1:13">
+      <x:c r="L819" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820" spans="1:13">
+      <x:c r="L820" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821" spans="1:13">
+      <x:c r="G821" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822" spans="1:13">
+      <x:c r="H822" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823" spans="1:13">
+      <x:c r="I823" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824" spans="1:13">
+      <x:c r="I824" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825" spans="1:13">
+      <x:c r="I825" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826" spans="1:13">
+      <x:c r="H826" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827" spans="1:13">
+      <x:c r="H827" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828" spans="1:13">
+      <x:c r="H828" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829" spans="1:13">
+      <x:c r="I829" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830" spans="1:13">
+      <x:c r="J830" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831" spans="1:13">
+      <x:c r="J831" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832" spans="1:13">
+      <x:c r="J832" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833" spans="1:13">
+      <x:c r="J833" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834" spans="1:13">
+      <x:c r="J834" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835" spans="1:13">
+      <x:c r="H835" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836" spans="1:13">
+      <x:c r="I836" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837" spans="1:13">
+      <x:c r="J837" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838" spans="1:13">
+      <x:c r="J838" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="839" spans="1:13">
+      <x:c r="K839" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="840" spans="1:13">
+      <x:c r="L840" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="841" spans="1:13">
+      <x:c r="L841" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="842" spans="1:13">
+      <x:c r="L842" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="843" spans="1:13">
+      <x:c r="L843" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="844" spans="1:13">
+      <x:c r="L844" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="845" spans="1:13">
+      <x:c r="L845" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="846" spans="1:13">
+      <x:c r="L846" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="847" spans="1:13">
+      <x:c r="G847" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="848" spans="1:13">
+      <x:c r="H848" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="849" spans="1:13">
+      <x:c r="I849" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="850" spans="1:13">
+      <x:c r="I850" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="851" spans="1:13">
+      <x:c r="I851" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="852" spans="1:13">
+      <x:c r="H852" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="853" spans="1:13">
+      <x:c r="H853" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="854" spans="1:13">
+      <x:c r="H854" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="855" spans="1:13">
+      <x:c r="I855" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="856" spans="1:13">
+      <x:c r="J856" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="857" spans="1:13">
+      <x:c r="J857" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="858" spans="1:13">
+      <x:c r="J858" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="859" spans="1:13">
+      <x:c r="J859" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="860" spans="1:13">
+      <x:c r="J860" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="861" spans="1:13">
+      <x:c r="H861" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="862" spans="1:13">
+      <x:c r="I862" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="863" spans="1:13">
+      <x:c r="J863" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="864" spans="1:13">
+      <x:c r="J864" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="865" spans="1:13">
+      <x:c r="K865" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="866" spans="1:13">
+      <x:c r="L866" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="867" spans="1:13">
+      <x:c r="L867" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="868" spans="1:13">
+      <x:c r="L868" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869" spans="1:13">
+      <x:c r="L869" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="870" spans="1:13">
+      <x:c r="L870" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="871" spans="1:13">
+      <x:c r="L871" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="872" spans="1:13">
+      <x:c r="L872" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="873" spans="1:13">
+      <x:c r="G873" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="874" spans="1:13">
+      <x:c r="H874" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="875" spans="1:13">
+      <x:c r="I875" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="876" spans="1:13">
+      <x:c r="I876" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="877" spans="1:13">
+      <x:c r="I877" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="878" spans="1:13">
+      <x:c r="H878" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="879" spans="1:13">
+      <x:c r="H879" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="880" spans="1:13">
+      <x:c r="H880" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="881" spans="1:13">
+      <x:c r="I881" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="882" spans="1:13">
+      <x:c r="J882" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883" spans="1:13">
+      <x:c r="J883" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884" spans="1:13">
+      <x:c r="J884" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="885" spans="1:13">
+      <x:c r="J885" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="886" spans="1:13">
+      <x:c r="J886" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="887" spans="1:13">
+      <x:c r="H887" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="888" spans="1:13">
+      <x:c r="I888" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889" spans="1:13">
+      <x:c r="J889" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="890" spans="1:13">
+      <x:c r="J890" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="891" spans="1:13">
+      <x:c r="K891" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="892" spans="1:13">
+      <x:c r="L892" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="893" spans="1:13">
+      <x:c r="L893" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="894" spans="1:13">
+      <x:c r="L894" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="895" spans="1:13">
+      <x:c r="L895" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="896" spans="1:13">
+      <x:c r="L896" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="897" spans="1:13">
+      <x:c r="L897" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="898" spans="1:13">
+      <x:c r="L898" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="899" spans="1:13">
+      <x:c r="G899" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="900" spans="1:13">
+      <x:c r="H900" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="901" spans="1:13">
+      <x:c r="I901" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="902" spans="1:13">
+      <x:c r="I902" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="903" spans="1:13">
+      <x:c r="I903" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="904" spans="1:13">
+      <x:c r="H904" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="905" spans="1:13">
+      <x:c r="H905" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="906" spans="1:13">
+      <x:c r="H906" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="907" spans="1:13">
+      <x:c r="I907" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="908" spans="1:13">
+      <x:c r="J908" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="909" spans="1:13">
+      <x:c r="J909" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="910" spans="1:13">
+      <x:c r="J910" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="911" spans="1:13">
+      <x:c r="J911" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="912" spans="1:13">
+      <x:c r="J912" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="913" spans="1:13">
+      <x:c r="H913" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="914" spans="1:13">
+      <x:c r="I914" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="915" spans="1:13">
+      <x:c r="J915" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="916" spans="1:13">
+      <x:c r="J916" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="917" spans="1:13">
+      <x:c r="K917" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="918" spans="1:13">
+      <x:c r="L918" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="919" spans="1:13">
+      <x:c r="L919" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="920" spans="1:13">
+      <x:c r="L920" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="921" spans="1:13">
+      <x:c r="L921" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="922" spans="1:13">
+      <x:c r="L922" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="923" spans="1:13">
+      <x:c r="L923" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="924" spans="1:13">
+      <x:c r="L924" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="925" spans="1:13">
+      <x:c r="G925" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="926" spans="1:13">
+      <x:c r="H926" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="927" spans="1:13">
+      <x:c r="I927" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="928" spans="1:13">
+      <x:c r="I928" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="929" spans="1:13">
+      <x:c r="I929" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="930" spans="1:13">
+      <x:c r="H930" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="931" spans="1:13">
+      <x:c r="H931" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="932" spans="1:13">
+      <x:c r="H932" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="933" spans="1:13">
+      <x:c r="I933" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="934" spans="1:13">
+      <x:c r="J934" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="935" spans="1:13">
+      <x:c r="J935" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="936" spans="1:13">
+      <x:c r="J936" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="937" spans="1:13">
+      <x:c r="J937" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="938" spans="1:13">
+      <x:c r="J938" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="939" spans="1:13">
+      <x:c r="H939" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="940" spans="1:13">
+      <x:c r="I940" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="941" spans="1:13">
+      <x:c r="J941" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="942" spans="1:13">
+      <x:c r="J942" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="943" spans="1:13">
+      <x:c r="K943" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="944" spans="1:13">
+      <x:c r="L944" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="945" spans="1:13">
+      <x:c r="L945" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="946" spans="1:13">
+      <x:c r="L946" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="947" spans="1:13">
+      <x:c r="L947" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="948" spans="1:13">
+      <x:c r="L948" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="949" spans="1:13">
+      <x:c r="L949" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="950" spans="1:13">
+      <x:c r="L950" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="951" spans="1:13">
+      <x:c r="G951" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="952" spans="1:13">
+      <x:c r="H952" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="953" spans="1:13">
+      <x:c r="I953" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="954" spans="1:13">
+      <x:c r="I954" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="955" spans="1:13">
+      <x:c r="I955" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="956" spans="1:13">
+      <x:c r="H956" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="957" spans="1:13">
+      <x:c r="H957" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="958" spans="1:13">
+      <x:c r="H958" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="959" spans="1:13">
+      <x:c r="I959" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="960" spans="1:13">
+      <x:c r="J960" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961" spans="1:13">
+      <x:c r="J961" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962" spans="1:13">
+      <x:c r="J962" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963" spans="1:13">
+      <x:c r="J963" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964" spans="1:13">
+      <x:c r="J964" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965" spans="1:13">
+      <x:c r="H965" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966" spans="1:13">
+      <x:c r="I966" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967" spans="1:13">
+      <x:c r="J967" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968" spans="1:13">
+      <x:c r="J968" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969" spans="1:13">
+      <x:c r="K969" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970" spans="1:13">
+      <x:c r="L970" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971" spans="1:13">
+      <x:c r="L971" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972" spans="1:13">
+      <x:c r="L972" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973" spans="1:13">
+      <x:c r="L973" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974" spans="1:13">
+      <x:c r="L974" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975" spans="1:13">
+      <x:c r="L975" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976" spans="1:13">
+      <x:c r="L976" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977" spans="1:13">
+      <x:c r="G977" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978" spans="1:13">
+      <x:c r="H978" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979" spans="1:13">
+      <x:c r="I979" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980" spans="1:13">
+      <x:c r="I980" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981" spans="1:13">
+      <x:c r="H981" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982" spans="1:13">
+      <x:c r="H982" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983" spans="1:13">
+      <x:c r="H983" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984" spans="1:13">
+      <x:c r="I984" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="985" spans="1:13">
+      <x:c r="J985" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="986" spans="1:13">
+      <x:c r="J986" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="987" spans="1:13">
+      <x:c r="J987" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="988" spans="1:13">
+      <x:c r="J988" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="989" spans="1:13">
+      <x:c r="J989" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="990" spans="1:13">
+      <x:c r="H990" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991" spans="1:13">
+      <x:c r="I991" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992" spans="1:13">
+      <x:c r="J992" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="993" spans="1:13">
+      <x:c r="J993" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="994" spans="1:13">
+      <x:c r="K994" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="995" spans="1:13">
+      <x:c r="L995" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996" spans="1:13">
+      <x:c r="L996" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997" spans="1:13">
+      <x:c r="L997" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998" spans="1:13">
+      <x:c r="L998" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999" spans="1:13">
+      <x:c r="L999" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000" spans="1:13">
+      <x:c r="L1000" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001" spans="1:13">
+      <x:c r="L1001" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002" spans="1:13">
+      <x:c r="K1002" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003" spans="1:13">
+      <x:c r="L1003" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004" spans="1:13">
+      <x:c r="L1004" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005" spans="1:13">
+      <x:c r="L1005" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006" spans="1:13">
+      <x:c r="L1006" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007" spans="1:13">
+      <x:c r="L1007" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008" spans="1:13">
+      <x:c r="L1008" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009" spans="1:13">
+      <x:c r="M1009" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010" spans="1:13">
+      <x:c r="M1010" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011" spans="1:13">
+      <x:c r="M1011" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012" spans="1:13">
+      <x:c r="M1012" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013" spans="1:13">
+      <x:c r="M1013" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014" spans="1:13">
+      <x:c r="M1014" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015" spans="1:13">
+      <x:c r="M1015" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016" spans="1:13">
+      <x:c r="M1016" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017" spans="1:13">
+      <x:c r="L1017" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018" spans="1:13">
+      <x:c r="L1018" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019" spans="1:13">
+      <x:c r="G1019" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020" spans="1:13">
+      <x:c r="H1020" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021" spans="1:13">
+      <x:c r="I1021" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022" spans="1:13">
+      <x:c r="I1022" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023" spans="1:13">
+      <x:c r="I1023" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024" spans="1:13">
+      <x:c r="H1024" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025" spans="1:13">
+      <x:c r="H1025" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026" spans="1:13">
+      <x:c r="H1026" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027" spans="1:13">
+      <x:c r="I1027" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028" spans="1:13">
+      <x:c r="J1028" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029" spans="1:13">
+      <x:c r="J1029" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030" spans="1:13">
+      <x:c r="J1030" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031" spans="1:13">
+      <x:c r="J1031" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032" spans="1:13">
+      <x:c r="J1032" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033" spans="1:13">
+      <x:c r="H1033" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034" spans="1:13">
+      <x:c r="I1034" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035" spans="1:13">
+      <x:c r="J1035" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036" spans="1:13">
+      <x:c r="J1036" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037" spans="1:13">
+      <x:c r="K1037" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038" spans="1:13">
+      <x:c r="L1038" s="1" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039" spans="1:13">
+      <x:c r="L1039" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040" spans="1:13">
+      <x:c r="L1040" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041" spans="1:13">
+      <x:c r="L1041" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042" spans="1:13">
+      <x:c r="L1042" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043" spans="1:13">
+      <x:c r="L1043" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1044" spans="1:13">
+      <x:c r="L1044" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1045" spans="1:13">
+      <x:c r="G1045" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1046" spans="1:13">
+      <x:c r="H1046" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1047" spans="1:13">
+      <x:c r="H1047" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1048" spans="1:13">
+      <x:c r="H1048" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
